--- a/XLibur.Tests/Resource/Other/PivotTable/Style/Style_values_at_intersection_of_row_and_column.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTable/Style/Style_values_at_intersection_of_row_and_column.xlsx
@@ -132,27 +132,30 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pivot table" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="4">
-    <pivotField name="Name" axis="axisRow" showAll="0" defaultSubtotal="0" sumSubtotal="1">
+    <pivotField name="Name" axis="axisRow" showAll="0" sumSubtotal="1">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+        <item t="sum"/>
+      </items>
+    </pivotField>
+    <pivotField name="Flavor" axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Month" axis="axisRow" showAll="0">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
-        <item t="sum"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField name="Flavor" axis="axisCol" showAll="0" defaultSubtotal="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField name="Month" axis="axisRow" showAll="0" defaultSubtotal="0">
-      <items count="2">
-        <item x="0"/>
-        <item x="1"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="0"/>

--- a/XLibur.Tests/Resource/Other/PivotTable/Style/Style_values_at_intersection_of_row_and_column.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTable/Style/Style_values_at_intersection_of_row_and_column.xlsx
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pivot table" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pivot table" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="4">
     <pivotField name="Name" axis="axisRow" showAll="0" sumSubtotal="1">
